--- a/User/SR/submission/RULulalla_validation.xlsx
+++ b/User/SR/submission/RULulalla_validation.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15408</v>
+        <v>16632</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48780</v>
+        <v>49860</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32616</v>
+        <v>33624</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12420</v>
+        <v>13068</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15192</v>
+        <v>16236</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11772</v>
+        <v>12348</v>
       </c>
     </row>
   </sheetData>
